--- a/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_2_biases.xlsx
+++ b/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_2_biases.xlsx
@@ -437,7 +437,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.01912898699996189</v>
+        <v>-0.01912898699996188</v>
       </c>
     </row>
     <row r="3">
